--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/01_Tasarım Girdileri, Malzeme ve Ürün Ağacı/EKG-TAS-PLN-02_urun_tasarim_girdileri_ve_validasyon_takvimi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/01_Tasarım Girdileri, Malzeme ve Ürün Ağacı/EKG-TAS-PLN-02_urun_tasarim_girdileri_ve_validasyon_takvimi.xlsx
@@ -716,7 +716,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Ürün Tasarım Girdileri ve Validasyon Takvimi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 08.09.2026
+Revizyon nedeni: Tasarım girdileri kontrollü kaynak ve test kimliğine bağlandı; değerlendirme ve gecikme takibi düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -875,7 +876,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Ürün Tasarım Girdileri ve Validasyon Takvimi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 08.09.2026
+Revizyon nedeni: Tasarım girdileri kontrollü kaynak ve test kimliğine bağlandı; değerlendirme ve gecikme takibi düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>